--- a/data_lake/industry/Semiconductor/Semiconductor CAPEX.xlsx
+++ b/data_lake/industry/Semiconductor/Semiconductor CAPEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\Documents\카카오톡 받은 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/Semiconductor/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53F20BA7-E781-439A-AC61-2481D9EAA0F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C17CCC2-5B3F-2E4F-AECC-8CCB464F3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{B97D0799-1BEB-42F8-9155-C74C2C96C56E}"/>
+    <workbookView xWindow="25220" yWindow="600" windowWidth="25980" windowHeight="25060" activeTab="4" xr2:uid="{B97D0799-1BEB-42F8-9155-C74C2C96C56E}"/>
   </bookViews>
   <sheets>
     <sheet name="NAND" sheetId="1" r:id="rId1"/>
@@ -305,9 +305,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -325,7 +325,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1704,7 +1704,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2652,7 +2652,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="ko-KR"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6154,19 +6154,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320E3B93-495F-4935-A97E-1BC8526B9AB5}">
   <dimension ref="A1:K27"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -6201,37 +6201,37 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>36891</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>37256</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>37621</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>37986</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>38352</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>38717</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>39082</v>
       </c>
@@ -6245,7 +6245,7 @@
         <v>3106.25</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>39447</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>3150.85</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>39813</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>40178</v>
       </c>
@@ -6287,7 +6287,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>40543</v>
       </c>
@@ -6301,7 +6301,7 @@
         <v>2696</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>40908</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>2460</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>41274</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>1963</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>41639</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>2044.3</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>42004</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>42369</v>
       </c>
@@ -6371,7 +6371,7 @@
         <v>2437.84</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>42735</v>
       </c>
@@ -6385,7 +6385,7 @@
         <v>3452.3</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>43100</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>5109.6000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>43465</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>43830</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>44196</v>
       </c>
@@ -6459,7 +6459,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>44561</v>
       </c>
@@ -6479,7 +6479,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>44926</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>45291</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>45657</v>
       </c>
@@ -6539,7 +6539,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>46022</v>
       </c>
@@ -6567,23 +6567,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9685AAB-EA34-486F-A5BC-A913C5F07A56}">
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.77734375" style="1"/>
-    <col min="12" max="12" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.77734375" style="1"/>
-    <col min="14" max="14" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.83203125" style="1"/>
+    <col min="12" max="12" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" style="1"/>
+    <col min="14" max="14" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>36891</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>37256</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>37621</v>
       </c>
@@ -6723,7 +6723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>37986</v>
       </c>
@@ -6755,7 +6755,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>38352</v>
       </c>
@@ -6787,7 +6787,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>38717</v>
       </c>
@@ -6819,7 +6819,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>39082</v>
       </c>
@@ -6851,7 +6851,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>39447</v>
       </c>
@@ -6886,7 +6886,7 @@
         <v>241.4</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>39813</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>454.1</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>40178</v>
       </c>
@@ -6950,7 +6950,7 @@
         <v>88.313000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>40543</v>
       </c>
@@ -6982,7 +6982,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>40908</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>198.21430000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>41274</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>101.7657</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>41639</v>
       </c>
@@ -7078,7 +7078,7 @@
         <v>69.707899999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>42004</v>
       </c>
@@ -7110,7 +7110,7 @@
         <v>430.0256</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>42369</v>
       </c>
@@ -7139,7 +7139,7 @@
         <v>123.0916</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>42735</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>148.9402</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>43100</v>
       </c>
@@ -7197,7 +7197,7 @@
         <v>499.92230000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>43465</v>
       </c>
@@ -7229,7 +7229,7 @@
         <v>554.6078</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>43830</v>
       </c>
@@ -7261,7 +7261,7 @@
         <v>424.39920000000001</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>44196</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>267.77449999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>44561</v>
       </c>
@@ -7325,7 +7325,7 @@
         <v>336.45139999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>44926</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>1473.181</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>45291</v>
       </c>
@@ -7389,7 +7389,7 @@
         <v>417.27120000000002</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>45657</v>
       </c>
@@ -7421,7 +7421,7 @@
         <v>482.80680000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>46022</v>
       </c>
@@ -7461,22 +7461,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1809E1-8742-45D5-8384-0B8CBD4B91B0}">
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.77734375" style="1"/>
+    <col min="1" max="1" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="1"/>
     <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="8.77734375" style="1"/>
-    <col min="15" max="15" width="9.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.77734375" style="1"/>
+    <col min="9" max="9" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="8.83203125" style="1"/>
+    <col min="15" max="15" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -7526,87 +7526,87 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>36891</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>37256</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>37621</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>37986</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>38352</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>38717</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>39082</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>39447</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>39813</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>40178</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>40543</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>40908</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>41274</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>41639</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>42004</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>42369</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>42735</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>10105</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>43100</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>11127</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>43465</v>
       </c>
@@ -7654,7 +7654,7 @@
         <v>650.73940000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>43830</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>534.69730000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>44196</v>
       </c>
@@ -7730,7 +7730,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>44561</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>44926</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>45291</v>
       </c>
@@ -7850,7 +7850,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>45657</v>
       </c>
@@ -7891,7 +7891,7 @@
         <v>2858</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>46022</v>
       </c>
@@ -7940,7 +7940,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1ACCD2-1A48-4153-9D3A-8CF140E4CA91}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7950,12 +7950,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365F0AC2-65A4-4AE7-B202-A8AA169AE8AB}">
   <dimension ref="A2:C32"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -7963,18 +7963,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -7990,7 +7990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -7998,7 +7998,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -8006,7 +8006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -8014,7 +8014,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -8041,7 +8041,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>0</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -8057,7 +8057,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -8065,7 +8065,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>26</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -8081,7 +8081,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>31</v>
       </c>
@@ -8089,7 +8089,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>12</v>
       </c>
@@ -8097,7 +8097,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -8105,7 +8105,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>35</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B22" t="s">
         <v>45</v>
       </c>
@@ -8132,12 +8132,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -8145,7 +8145,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
         <v>50</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>31</v>
       </c>
@@ -8161,7 +8161,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>26</v>
       </c>
@@ -8169,7 +8169,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>54</v>
       </c>
@@ -8177,7 +8177,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>57</v>
       </c>
@@ -8185,7 +8185,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>59</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
         <v>61</v>
       </c>
@@ -8201,7 +8201,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>63</v>
       </c>
@@ -8213,6 +8213,7 @@
   <hyperlinks>
     <hyperlink ref="C21" r:id="rId1" xr:uid="{99441D84-9010-4F4E-AFC0-F8D2F1C2F414}"/>
     <hyperlink ref="C20" r:id="rId2" xr:uid="{A7DFB6A2-9751-47B6-AD2B-8EA20FFB904C}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{F460ACC2-F850-DF46-97BD-159ABA654FED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data_lake/industry/Semiconductor/Semiconductor CAPEX.xlsx
+++ b/data_lake/industry/Semiconductor/Semiconductor CAPEX.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/FinancialData/data_lake/industry/Semiconductor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data_lake\industry\Semiconductor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C17CCC2-5B3F-2E4F-AECC-8CCB464F3EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B9DFD3-1429-4D15-AEC1-84FDA0D33415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25220" yWindow="600" windowWidth="25980" windowHeight="25060" activeTab="4" xr2:uid="{B97D0799-1BEB-42F8-9155-C74C2C96C56E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="2" xr2:uid="{B97D0799-1BEB-42F8-9155-C74C2C96C56E}"/>
   </bookViews>
   <sheets>
-    <sheet name="NAND" sheetId="1" r:id="rId1"/>
-    <sheet name="DRAM" sheetId="4" r:id="rId2"/>
+    <sheet name="DRAM" sheetId="4" r:id="rId1"/>
+    <sheet name="NAND" sheetId="1" r:id="rId2"/>
     <sheet name="FOUNDRY" sheetId="5" r:id="rId3"/>
     <sheet name="fig" sheetId="3" r:id="rId4"/>
     <sheet name="info" sheetId="2" r:id="rId5"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="65">
   <si>
     <t>SK Hynix</t>
   </si>
@@ -234,6 +234,9 @@
   <si>
     <t>UMC</t>
   </si>
+  <si>
+    <t>YMTC</t>
+  </si>
 </sst>
 </file>
 
@@ -290,7 +293,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -302,6 +305,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1251,7 +1257,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1451,8 +1457,8 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="1626255440"/>
-        <c:axId val="1238670000"/>
+        <c:axId val="1257176400"/>
+        <c:axId val="1238665680"/>
       </c:lineChart>
       <c:dateAx>
         <c:axId val="1257176400"/>
@@ -1564,65 +1570,6 @@
         <c:crossBetween val="between"/>
         <c:majorUnit val="10000"/>
       </c:valAx>
-      <c:valAx>
-        <c:axId val="1238670000"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1626255440"/>
-        <c:crosses val="max"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:dateAx>
-        <c:axId val="1626255440"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="yyyy\-mm\-dd;@" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1238670000"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="years"/>
-      </c:dateAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1784,10 +1731,10 @@
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
-          <c:order val="0"/>
+          <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>NAND!$E$1</c:f>
+              <c:f>NAND!$F$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1895,7 +1842,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NAND!$E$2:$E$27</c:f>
+              <c:f>NAND!$F$2:$F$27</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="26"/>
@@ -1970,10 +1917,10 @@
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
-          <c:order val="1"/>
+          <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>NAND!$F$1</c:f>
+              <c:f>NAND!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2081,7 +2028,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NAND!$F$2:$F$27</c:f>
+              <c:f>NAND!$G$2:$G$27</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="26"/>
@@ -2156,10 +2103,10 @@
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
-          <c:order val="2"/>
+          <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>NAND!$G$1</c:f>
+              <c:f>NAND!$H$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2267,7 +2214,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NAND!$G$2:$G$27</c:f>
+              <c:f>NAND!$H$2:$H$27</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="26"/>
@@ -2300,10 +2247,10 @@
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
-          <c:order val="3"/>
+          <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>NAND!$J$1</c:f>
+              <c:f>NAND!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2411,7 +2358,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>NAND!$J$2:$J$27</c:f>
+              <c:f>NAND!$K$2:$K$27</c:f>
               <c:numCache>
                 <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="26"/>
@@ -2445,6 +2392,63 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-C1CF-4A54-959D-2B2F970749AF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>NAND!$M$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> YMTC </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>NAND!$M$2:$M$27</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="20">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B7AE-4B88-BD20-B8277E2AE25B}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2461,6 +2465,124 @@
         <c:axId val="1270699456"/>
         <c:axId val="1112038640"/>
       </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>NAND!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v> Total </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>NAND!$E$2:$E$27</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0.0_);_(* \(#,##0.0\);_(* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="26"/>
+                <c:pt idx="6">
+                  <c:v>9819.2999999999993</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>10027.41</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7218</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3048</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>6441</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8814</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8445.2000000000007</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>8064.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9655</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9002.3989999999994</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12172.2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>25439.599999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>23061.75</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20050</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21600</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>29600</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>32395</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>18200</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19500</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>21100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B7AE-4B88-BD20-B8277E2AE25B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1270699456"/>
+        <c:axId val="1112038640"/>
+      </c:lineChart>
       <c:dateAx>
         <c:axId val="1270699456"/>
         <c:scaling>
@@ -2512,7 +2634,6 @@
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="years"/>
-        <c:majorUnit val="2"/>
         <c:majorTimeUnit val="years"/>
       </c:dateAx>
       <c:valAx>
@@ -3655,7 +3776,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="tx1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -6152,411 +6273,892 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320E3B93-495F-4935-A97E-1BC8526B9AB5}">
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9685AAB-EA34-486F-A5BC-A913C5F07A56}">
+  <dimension ref="A1:P27"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.1640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="10.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.1796875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.81640625" style="1"/>
+    <col min="12" max="12" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.81640625" style="1"/>
+    <col min="14" max="14" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>42</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>36891</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E2" s="1">
+        <v>10451</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2500</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1680</v>
+      </c>
+      <c r="I2" s="1">
+        <v>651.84849999999994</v>
+      </c>
+      <c r="K2" s="1">
+        <v>87</v>
+      </c>
+      <c r="M2" s="1">
+        <v>325</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1125</v>
+      </c>
+      <c r="P2" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>37256</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E3" s="1">
+        <v>7580</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1950</v>
+      </c>
+      <c r="H3" s="1">
+        <v>350</v>
+      </c>
+      <c r="I3" s="1">
+        <v>321.77699999999999</v>
+      </c>
+      <c r="K3" s="1">
+        <v>152</v>
+      </c>
+      <c r="M3" s="1">
+        <v>155</v>
+      </c>
+      <c r="N3" s="1">
+        <v>1350</v>
+      </c>
+      <c r="P3" s="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>37621</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E4" s="1">
+        <v>5500</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1200</v>
+      </c>
+      <c r="H4" s="1">
+        <v>350</v>
+      </c>
+      <c r="I4" s="1">
+        <v>121.1305</v>
+      </c>
+      <c r="K4" s="1">
+        <v>118</v>
+      </c>
+      <c r="L4" s="1">
+        <v>7</v>
+      </c>
+      <c r="M4" s="1">
+        <v>264</v>
+      </c>
+      <c r="N4" s="1">
+        <v>600</v>
+      </c>
+      <c r="P4" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>37986</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E5" s="1">
+        <v>6650</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2154</v>
+      </c>
+      <c r="H5" s="1">
+        <v>650</v>
+      </c>
+      <c r="I5" s="1">
+        <v>195.17660000000001</v>
+      </c>
+      <c r="K5" s="1">
+        <v>380</v>
+      </c>
+      <c r="L5" s="1">
+        <v>460</v>
+      </c>
+      <c r="M5" s="1">
+        <v>450</v>
+      </c>
+      <c r="N5" s="1">
+        <v>900</v>
+      </c>
+      <c r="P5" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>38352</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E6" s="1">
+        <v>10732.28</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2900</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1400</v>
+      </c>
+      <c r="I6" s="1">
+        <v>206.05340000000001</v>
+      </c>
+      <c r="K6" s="1">
+        <v>130</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1139</v>
+      </c>
+      <c r="M6" s="1">
+        <v>861</v>
+      </c>
+      <c r="N6" s="1">
+        <v>1231</v>
+      </c>
+      <c r="P6" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>38717</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="E7" s="1">
+        <v>12972</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2800</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2120</v>
+      </c>
+      <c r="I7" s="1">
+        <v>80</v>
+      </c>
+      <c r="K7" s="1">
+        <v>150</v>
+      </c>
+      <c r="L7" s="1">
+        <v>718</v>
+      </c>
+      <c r="M7" s="1">
+        <v>1500</v>
+      </c>
+      <c r="N7" s="1">
+        <v>1500</v>
+      </c>
+      <c r="P7" s="1">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>39082</v>
       </c>
       <c r="E8" s="1">
-        <v>2550.5369999999998</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3053.5149999999999</v>
+        <v>16541.689999999999</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3621</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3656</v>
       </c>
       <c r="I8" s="1">
-        <v>3106.25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+      <c r="K8" s="1">
+        <v>180</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1415</v>
+      </c>
+      <c r="M8" s="1">
+        <v>2314</v>
+      </c>
+      <c r="N8" s="1">
+        <v>1300</v>
+      </c>
+      <c r="P8" s="1">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>39447</v>
       </c>
       <c r="E9" s="1">
-        <v>1033.3689999999999</v>
-      </c>
-      <c r="F9" s="1">
-        <v>3089.3429999999998</v>
+        <v>21439.78</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4137</v>
+      </c>
+      <c r="H9" s="1">
+        <v>3810</v>
       </c>
       <c r="I9" s="1">
-        <v>3150.85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1431.64</v>
+      </c>
+      <c r="K9" s="1">
+        <v>50</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1340.3</v>
+      </c>
+      <c r="M9" s="1">
+        <v>1931.2</v>
+      </c>
+      <c r="N9" s="1">
+        <v>1600</v>
+      </c>
+      <c r="O9" s="1">
+        <v>2892.5</v>
+      </c>
+      <c r="P9" s="1">
+        <v>241.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>39813</v>
       </c>
       <c r="E10" s="1">
-        <v>591</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2545</v>
+        <v>12246.19</v>
+      </c>
+      <c r="G10" s="1">
+        <v>4278.5119999999997</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1902</v>
       </c>
       <c r="I10" s="1">
-        <v>2843</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>380.59</v>
+      </c>
+      <c r="L10" s="1">
+        <v>624.79999999999995</v>
+      </c>
+      <c r="M10" s="1">
+        <v>644.11</v>
+      </c>
+      <c r="N10" s="1">
+        <v>900</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1159.4100000000001</v>
+      </c>
+      <c r="P10" s="1">
+        <v>454.1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>40178</v>
       </c>
       <c r="E11" s="1">
-        <v>243</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1293</v>
+        <v>4336.2359999999999</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1000</v>
+      </c>
+      <c r="H11" s="1">
+        <v>700</v>
       </c>
       <c r="I11" s="1">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <v>382.69</v>
+      </c>
+      <c r="L11" s="1">
+        <v>396.73480000000001</v>
+      </c>
+      <c r="M11" s="1">
+        <v>207</v>
+      </c>
+      <c r="N11" s="1">
+        <v>385</v>
+      </c>
+      <c r="O11" s="1">
+        <v>104</v>
+      </c>
+      <c r="P11" s="1">
+        <v>88.313000000000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>40543</v>
       </c>
       <c r="E12" s="1">
-        <v>730</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2730</v>
+        <v>11897.11</v>
+      </c>
+      <c r="G12" s="1">
+        <v>4218.75</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1978</v>
       </c>
       <c r="I12" s="1">
-        <v>2696</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <v>767</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1833</v>
+      </c>
+      <c r="M12" s="1">
+        <v>233</v>
+      </c>
+      <c r="N12" s="1">
+        <v>700</v>
+      </c>
+      <c r="O12" s="1">
+        <v>427</v>
+      </c>
+      <c r="P12" s="1">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>40908</v>
       </c>
       <c r="E13" s="1">
-        <v>921</v>
-      </c>
-      <c r="F13" s="1">
-        <v>3500</v>
+        <v>8132.5</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2412.8679999999999</v>
+      </c>
+      <c r="H13" s="1">
+        <v>2126.8989999999999</v>
       </c>
       <c r="I13" s="1">
-        <v>2460</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <v>360.44970000000001</v>
+      </c>
+      <c r="L13" s="1">
+        <v>383.59789999999998</v>
+      </c>
+      <c r="M13" s="1">
+        <v>339</v>
+      </c>
+      <c r="N13" s="1">
+        <v>1016</v>
+      </c>
+      <c r="O13" s="1">
+        <v>264.517</v>
+      </c>
+      <c r="P13" s="1">
+        <v>198.21430000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>41274</v>
       </c>
       <c r="E14" s="1">
-        <v>1569.2</v>
-      </c>
-      <c r="F14" s="1">
-        <v>3579</v>
+        <v>5960.4830000000002</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2126.7359999999999</v>
+      </c>
+      <c r="H14" s="1">
+        <v>2187.5</v>
       </c>
       <c r="I14" s="1">
-        <v>1963</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+        <v>67.663300000000007</v>
+      </c>
+      <c r="L14" s="1">
+        <v>145.47620000000001</v>
+      </c>
+      <c r="M14" s="1">
+        <v>84.260199999999998</v>
+      </c>
+      <c r="N14" s="1">
+        <v>554.33330000000001</v>
+      </c>
+      <c r="O14" s="1">
+        <v>125</v>
+      </c>
+      <c r="P14" s="1">
+        <v>101.7657</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>41639</v>
       </c>
       <c r="E15" s="1">
-        <v>1342</v>
-      </c>
-      <c r="F15" s="1">
-        <v>3958.2</v>
+        <v>7654.085</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3600</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2129.741</v>
       </c>
       <c r="I15" s="1">
-        <v>2044.3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+        <v>189.00980000000001</v>
+      </c>
+      <c r="L15" s="1">
+        <v>215.62620000000001</v>
+      </c>
+      <c r="M15" s="1">
+        <v>70</v>
+      </c>
+      <c r="N15" s="1">
+        <v>950</v>
+      </c>
+      <c r="O15" s="1">
+        <v>180</v>
+      </c>
+      <c r="P15" s="1">
+        <v>69.707899999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>42004</v>
       </c>
       <c r="E16" s="1">
-        <v>1226.8</v>
-      </c>
-      <c r="F16" s="1">
-        <v>5140.2</v>
+        <v>9821.58</v>
+      </c>
+      <c r="G16" s="1">
+        <v>4100</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2659.348</v>
       </c>
       <c r="I16" s="1">
-        <v>2308</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+        <v>191.25450000000001</v>
+      </c>
+      <c r="L16" s="1">
+        <v>725.94880000000001</v>
+      </c>
+      <c r="M16" s="1">
+        <v>30</v>
+      </c>
+      <c r="N16" s="1">
+        <v>1525</v>
+      </c>
+      <c r="O16" s="1">
+        <v>160</v>
+      </c>
+      <c r="P16" s="1">
+        <v>430.0256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>42369</v>
       </c>
       <c r="E17" s="1">
-        <v>1142.03</v>
-      </c>
-      <c r="F17" s="1">
-        <v>4520.5290000000005</v>
+        <v>12459.52</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H17" s="1">
+        <v>3400</v>
       </c>
       <c r="I17" s="1">
-        <v>2437.84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+        <v>121.0758</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1795.348</v>
+      </c>
+      <c r="M17" s="1">
+        <v>120</v>
+      </c>
+      <c r="N17" s="1">
+        <v>1900</v>
+      </c>
+      <c r="P17" s="1">
+        <v>123.0916</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>42735</v>
       </c>
       <c r="E18" s="1">
-        <v>1472</v>
-      </c>
-      <c r="F18" s="1">
-        <v>4497.8999999999996</v>
+        <v>12124.01</v>
+      </c>
+      <c r="G18" s="1">
+        <v>4139.201</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4742.835</v>
       </c>
       <c r="I18" s="1">
-        <v>3452.3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+        <v>693.03740000000005</v>
+      </c>
+      <c r="L18" s="1">
+        <v>200</v>
+      </c>
+      <c r="M18" s="1">
+        <v>80</v>
+      </c>
+      <c r="N18" s="1">
+        <v>2120</v>
+      </c>
+      <c r="P18" s="1">
+        <v>148.9402</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>43100</v>
       </c>
       <c r="E19" s="1">
-        <v>4245</v>
-      </c>
-      <c r="F19" s="1">
-        <v>11735</v>
+        <v>14628.04</v>
+      </c>
+      <c r="G19" s="1">
+        <v>7000</v>
+      </c>
+      <c r="H19" s="1">
+        <v>4251.4920000000002</v>
       </c>
       <c r="I19" s="1">
-        <v>5109.6000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+        <v>966.62620000000004</v>
+      </c>
+      <c r="L19" s="1">
+        <v>140</v>
+      </c>
+      <c r="M19" s="1">
+        <v>70</v>
+      </c>
+      <c r="N19" s="1">
+        <v>1700</v>
+      </c>
+      <c r="P19" s="1">
+        <v>499.92230000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>43465</v>
       </c>
       <c r="E20" s="1">
-        <v>4881.75</v>
+        <v>19381.740000000002</v>
       </c>
       <c r="F20" s="1">
-        <v>7000</v>
+        <v>3826.0390000000002</v>
+      </c>
+      <c r="G20" s="1">
+        <v>9093.8459999999995</v>
       </c>
       <c r="H20" s="1">
-        <v>3000</v>
+        <v>5757</v>
       </c>
       <c r="I20" s="1">
-        <v>4880</v>
+        <v>676.28710000000001</v>
       </c>
       <c r="J20" s="1">
-        <v>3300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+        <v>1432</v>
+      </c>
+      <c r="M20" s="1">
+        <v>100</v>
+      </c>
+      <c r="N20" s="1">
+        <v>3200</v>
+      </c>
+      <c r="P20" s="1">
+        <v>554.6078</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>43830</v>
       </c>
       <c r="E21" s="1">
-        <v>4000</v>
+        <v>19091.28</v>
       </c>
       <c r="F21" s="1">
-        <v>7800</v>
+        <v>1448.0129999999999</v>
+      </c>
+      <c r="G21" s="1">
+        <v>8184.4610000000002</v>
       </c>
       <c r="H21" s="1">
-        <v>2000</v>
+        <v>5469.15</v>
       </c>
       <c r="I21" s="1">
-        <v>4050</v>
+        <v>177.25489999999999</v>
       </c>
       <c r="J21" s="1">
-        <v>2200</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="M21" s="1">
+        <v>70</v>
+      </c>
+      <c r="N21" s="1">
+        <v>3296</v>
+      </c>
+      <c r="P21" s="1">
+        <v>424.39920000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>44196</v>
       </c>
       <c r="E22" s="1">
-        <v>3000</v>
+        <v>18953.82</v>
       </c>
       <c r="F22" s="1">
-        <v>7900</v>
+        <v>2845</v>
       </c>
       <c r="G22" s="1">
-        <v>3800</v>
+        <v>8000</v>
       </c>
       <c r="H22" s="1">
-        <v>900</v>
+        <v>4500</v>
+      </c>
+      <c r="I22" s="1">
+        <v>287.64109999999999</v>
       </c>
       <c r="J22" s="1">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+      <c r="M22" s="1">
+        <v>60</v>
+      </c>
+      <c r="N22" s="1">
+        <v>2966.4</v>
+      </c>
+      <c r="P22" s="1">
+        <v>267.77449999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>44561</v>
       </c>
       <c r="E23" s="1">
-        <v>4000</v>
+        <v>28047.88</v>
       </c>
       <c r="F23" s="1">
-        <v>11200</v>
+        <v>1991.5</v>
       </c>
       <c r="G23" s="1">
-        <v>3700</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="1">
-        <v>1100</v>
+        <v>7950</v>
+      </c>
+      <c r="I23" s="1">
+        <v>403.0258</v>
       </c>
       <c r="J23" s="1">
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="M23" s="1">
+        <v>48</v>
+      </c>
+      <c r="N23" s="1">
+        <v>5300</v>
+      </c>
+      <c r="P23" s="1">
+        <v>336.45139999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>44926</v>
       </c>
       <c r="E24" s="1">
-        <v>4450</v>
+        <v>30035.93</v>
       </c>
       <c r="F24" s="1">
-        <v>12200</v>
+        <v>4340.607</v>
       </c>
       <c r="G24" s="1">
-        <v>4650</v>
+        <v>11700</v>
+      </c>
+      <c r="H24" s="1">
+        <v>6757.5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>694.64340000000004</v>
       </c>
       <c r="J24" s="1">
-        <v>4800</v>
-      </c>
-      <c r="K24" s="1">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+        <v>15</v>
+      </c>
+      <c r="M24" s="1">
+        <v>55</v>
+      </c>
+      <c r="N24" s="1">
+        <v>5000</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1473.181</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>45291</v>
       </c>
       <c r="E25" s="1">
-        <v>2000</v>
+        <v>19976.75</v>
       </c>
       <c r="F25" s="1">
+        <v>2083.491</v>
+      </c>
+      <c r="G25" s="1">
         <v>10000</v>
       </c>
-      <c r="G25" s="1">
-        <v>1800</v>
+      <c r="H25" s="1">
+        <v>4000</v>
+      </c>
+      <c r="I25" s="1">
+        <v>423.69080000000002</v>
       </c>
       <c r="J25" s="1">
-        <v>2000</v>
-      </c>
-      <c r="K25" s="1">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+        <v>10.5</v>
+      </c>
+      <c r="M25" s="1">
+        <v>41.8</v>
+      </c>
+      <c r="N25" s="1">
+        <v>3000</v>
+      </c>
+      <c r="P25" s="1">
+        <v>417.27120000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>45657</v>
       </c>
       <c r="E26" s="1">
-        <v>1800</v>
+        <v>29734.28</v>
       </c>
       <c r="F26" s="1">
-        <v>9500</v>
+        <v>3800</v>
       </c>
       <c r="G26" s="1">
-        <v>2300</v>
+        <v>13500</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6400</v>
+      </c>
+      <c r="I26" s="1">
+        <v>502.83550000000002</v>
       </c>
       <c r="J26" s="1">
-        <v>1800</v>
-      </c>
-      <c r="K26" s="1">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+        <v>8.9250000000000007</v>
+      </c>
+      <c r="M26" s="1">
+        <v>39.71</v>
+      </c>
+      <c r="N26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="P26" s="1">
+        <v>482.80680000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>46022</v>
       </c>
       <c r="E27" s="1">
-        <v>2200</v>
+        <v>53700</v>
       </c>
       <c r="F27" s="1">
-        <v>9000</v>
+        <v>6500</v>
       </c>
       <c r="G27" s="1">
-        <v>3200</v>
+        <v>18000</v>
+      </c>
+      <c r="H27" s="1">
+        <v>17500</v>
+      </c>
+      <c r="I27" s="1">
+        <v>429.70409999999998</v>
       </c>
       <c r="J27" s="1">
-        <v>1600</v>
-      </c>
-      <c r="K27" s="1">
-        <v>1200</v>
+        <v>20</v>
+      </c>
+      <c r="M27" s="1">
+        <v>42</v>
+      </c>
+      <c r="N27" s="1">
+        <v>11000</v>
+      </c>
+      <c r="P27" s="1">
+        <v>176.37110000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6565,892 +7167,496 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9685AAB-EA34-486F-A5BC-A913C5F07A56}">
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320E3B93-495F-4935-A97E-1BC8526B9AB5}">
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.1640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.1640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="8.83203125" style="1"/>
-    <col min="12" max="12" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.83203125" style="1"/>
-    <col min="14" max="14" width="9.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="10.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="9.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>20</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>36891</v>
       </c>
-      <c r="E2" s="1">
-        <v>10451</v>
-      </c>
-      <c r="G2" s="1">
-        <v>2500</v>
-      </c>
-      <c r="H2" s="1">
-        <v>1680</v>
-      </c>
-      <c r="I2" s="1">
-        <v>651.84849999999994</v>
-      </c>
-      <c r="K2" s="1">
-        <v>87</v>
-      </c>
-      <c r="M2" s="1">
-        <v>325</v>
-      </c>
-      <c r="N2" s="1">
-        <v>1125</v>
-      </c>
-      <c r="P2" s="1">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>37256</v>
       </c>
-      <c r="E3" s="1">
-        <v>7580</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1950</v>
-      </c>
-      <c r="H3" s="1">
-        <v>350</v>
-      </c>
-      <c r="I3" s="1">
-        <v>321.77699999999999</v>
-      </c>
-      <c r="K3" s="1">
-        <v>152</v>
-      </c>
-      <c r="M3" s="1">
-        <v>155</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1350</v>
-      </c>
-      <c r="P3" s="1">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>37621</v>
       </c>
-      <c r="E4" s="1">
-        <v>5500</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1200</v>
-      </c>
-      <c r="H4" s="1">
-        <v>350</v>
-      </c>
-      <c r="I4" s="1">
-        <v>121.1305</v>
-      </c>
-      <c r="K4" s="1">
-        <v>118</v>
-      </c>
-      <c r="L4" s="1">
-        <v>7</v>
-      </c>
-      <c r="M4" s="1">
-        <v>264</v>
-      </c>
-      <c r="N4" s="1">
-        <v>600</v>
-      </c>
-      <c r="P4" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>37986</v>
       </c>
-      <c r="E5" s="1">
-        <v>6650</v>
-      </c>
-      <c r="G5" s="1">
-        <v>2154</v>
-      </c>
-      <c r="H5" s="1">
-        <v>650</v>
-      </c>
-      <c r="I5" s="1">
-        <v>195.17660000000001</v>
-      </c>
-      <c r="K5" s="1">
-        <v>380</v>
-      </c>
-      <c r="L5" s="1">
-        <v>460</v>
-      </c>
-      <c r="M5" s="1">
-        <v>450</v>
-      </c>
-      <c r="N5" s="1">
-        <v>900</v>
-      </c>
-      <c r="P5" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>38352</v>
       </c>
-      <c r="E6" s="1">
-        <v>10732.28</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2900</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1400</v>
-      </c>
-      <c r="I6" s="1">
-        <v>206.05340000000001</v>
-      </c>
-      <c r="K6" s="1">
-        <v>130</v>
-      </c>
-      <c r="L6" s="1">
-        <v>1139</v>
-      </c>
-      <c r="M6" s="1">
-        <v>861</v>
-      </c>
-      <c r="N6" s="1">
-        <v>1231</v>
-      </c>
-      <c r="P6" s="1">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>38717</v>
       </c>
-      <c r="E7" s="1">
-        <v>12972</v>
-      </c>
-      <c r="G7" s="1">
-        <v>2800</v>
-      </c>
-      <c r="H7" s="1">
-        <v>2120</v>
-      </c>
-      <c r="I7" s="1">
-        <v>80</v>
-      </c>
-      <c r="K7" s="1">
-        <v>150</v>
-      </c>
-      <c r="L7" s="1">
-        <v>718</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1500</v>
-      </c>
-      <c r="N7" s="1">
-        <v>1500</v>
-      </c>
-      <c r="P7" s="1">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>39082</v>
       </c>
-      <c r="E8" s="1">
-        <v>16541.689999999999</v>
+      <c r="E8" s="6">
+        <v>9819.2999999999993</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2550.5369999999998</v>
       </c>
       <c r="G8" s="1">
-        <v>3621</v>
-      </c>
-      <c r="H8" s="1">
-        <v>3656</v>
-      </c>
-      <c r="I8" s="1">
-        <v>200</v>
-      </c>
-      <c r="K8" s="1">
-        <v>180</v>
-      </c>
-      <c r="L8" s="1">
-        <v>1415</v>
-      </c>
-      <c r="M8" s="1">
-        <v>2314</v>
-      </c>
-      <c r="N8" s="1">
-        <v>1300</v>
-      </c>
-      <c r="P8" s="1">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3053.5149999999999</v>
+      </c>
+      <c r="J8" s="1">
+        <v>3106.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>39447</v>
       </c>
-      <c r="E9" s="1">
-        <v>21439.78</v>
+      <c r="E9" s="6">
+        <v>10027.41</v>
+      </c>
+      <c r="F9" s="1">
+        <v>1033.3689999999999</v>
       </c>
       <c r="G9" s="1">
-        <v>4137</v>
-      </c>
-      <c r="H9" s="1">
-        <v>3810</v>
-      </c>
-      <c r="I9" s="1">
-        <v>1431.64</v>
-      </c>
-      <c r="K9" s="1">
-        <v>50</v>
-      </c>
-      <c r="L9" s="1">
-        <v>1340.3</v>
-      </c>
-      <c r="M9" s="1">
-        <v>1931.2</v>
-      </c>
-      <c r="N9" s="1">
-        <v>1600</v>
-      </c>
-      <c r="O9" s="1">
-        <v>2892.5</v>
-      </c>
-      <c r="P9" s="1">
-        <v>241.4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3089.3429999999998</v>
+      </c>
+      <c r="J9" s="1">
+        <v>3150.85</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>39813</v>
       </c>
-      <c r="E10" s="1">
-        <v>12246.19</v>
+      <c r="E10" s="6">
+        <v>7218</v>
+      </c>
+      <c r="F10" s="1">
+        <v>591</v>
       </c>
       <c r="G10" s="1">
-        <v>4278.5119999999997</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1902</v>
-      </c>
-      <c r="I10" s="1">
-        <v>380.59</v>
-      </c>
-      <c r="L10" s="1">
-        <v>624.79999999999995</v>
-      </c>
-      <c r="M10" s="1">
-        <v>644.11</v>
-      </c>
-      <c r="N10" s="1">
-        <v>900</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1159.4100000000001</v>
-      </c>
-      <c r="P10" s="1">
-        <v>454.1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2545</v>
+      </c>
+      <c r="J10" s="1">
+        <v>2843</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>40178</v>
       </c>
-      <c r="E11" s="1">
-        <v>4336.2359999999999</v>
+      <c r="E11" s="6">
+        <v>3048</v>
+      </c>
+      <c r="F11" s="1">
+        <v>243</v>
       </c>
       <c r="G11" s="1">
-        <v>1000</v>
-      </c>
-      <c r="H11" s="1">
-        <v>700</v>
-      </c>
-      <c r="I11" s="1">
-        <v>382.69</v>
-      </c>
-      <c r="L11" s="1">
-        <v>396.73480000000001</v>
-      </c>
-      <c r="M11" s="1">
-        <v>207</v>
-      </c>
-      <c r="N11" s="1">
-        <v>385</v>
-      </c>
-      <c r="O11" s="1">
-        <v>104</v>
-      </c>
-      <c r="P11" s="1">
-        <v>88.313000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1293</v>
+      </c>
+      <c r="J11" s="1">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>40543</v>
       </c>
-      <c r="E12" s="1">
-        <v>11897.11</v>
+      <c r="E12" s="6">
+        <v>6441</v>
+      </c>
+      <c r="F12" s="1">
+        <v>730</v>
       </c>
       <c r="G12" s="1">
-        <v>4218.75</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1978</v>
-      </c>
-      <c r="I12" s="1">
-        <v>767</v>
-      </c>
-      <c r="L12" s="1">
-        <v>1833</v>
-      </c>
-      <c r="M12" s="1">
-        <v>233</v>
-      </c>
-      <c r="N12" s="1">
-        <v>700</v>
-      </c>
-      <c r="O12" s="1">
-        <v>427</v>
-      </c>
-      <c r="P12" s="1">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+        <v>2730</v>
+      </c>
+      <c r="J12" s="1">
+        <v>2696</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>40908</v>
       </c>
-      <c r="E13" s="1">
-        <v>8132.5</v>
+      <c r="E13" s="6">
+        <v>8814</v>
+      </c>
+      <c r="F13" s="1">
+        <v>921</v>
       </c>
       <c r="G13" s="1">
-        <v>2412.8679999999999</v>
-      </c>
-      <c r="H13" s="1">
-        <v>2126.8989999999999</v>
-      </c>
-      <c r="I13" s="1">
-        <v>360.44970000000001</v>
-      </c>
-      <c r="L13" s="1">
-        <v>383.59789999999998</v>
-      </c>
-      <c r="M13" s="1">
-        <v>339</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1016</v>
-      </c>
-      <c r="O13" s="1">
-        <v>264.517</v>
-      </c>
-      <c r="P13" s="1">
-        <v>198.21430000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3500</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2460</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>41274</v>
       </c>
-      <c r="E14" s="1">
-        <v>5960.4830000000002</v>
+      <c r="E14" s="6">
+        <v>8445.2000000000007</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1569.2</v>
       </c>
       <c r="G14" s="1">
-        <v>2126.7359999999999</v>
-      </c>
-      <c r="H14" s="1">
-        <v>2187.5</v>
-      </c>
-      <c r="I14" s="1">
-        <v>67.663300000000007</v>
-      </c>
-      <c r="L14" s="1">
-        <v>145.47620000000001</v>
-      </c>
-      <c r="M14" s="1">
-        <v>84.260199999999998</v>
-      </c>
-      <c r="N14" s="1">
-        <v>554.33330000000001</v>
-      </c>
-      <c r="O14" s="1">
-        <v>125</v>
-      </c>
-      <c r="P14" s="1">
-        <v>101.7657</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3579</v>
+      </c>
+      <c r="J14" s="1">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>41639</v>
       </c>
-      <c r="E15" s="1">
-        <v>7654.085</v>
+      <c r="E15" s="6">
+        <v>8064.5</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1342</v>
       </c>
       <c r="G15" s="1">
-        <v>3600</v>
-      </c>
-      <c r="H15" s="1">
-        <v>2129.741</v>
-      </c>
-      <c r="I15" s="1">
-        <v>189.00980000000001</v>
-      </c>
-      <c r="L15" s="1">
-        <v>215.62620000000001</v>
-      </c>
-      <c r="M15" s="1">
-        <v>70</v>
-      </c>
-      <c r="N15" s="1">
-        <v>950</v>
-      </c>
-      <c r="O15" s="1">
-        <v>180</v>
-      </c>
-      <c r="P15" s="1">
-        <v>69.707899999999995</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3958.2</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2044.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>42004</v>
       </c>
-      <c r="E16" s="1">
-        <v>9821.58</v>
+      <c r="E16" s="6">
+        <v>9655</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1226.8</v>
       </c>
       <c r="G16" s="1">
-        <v>4100</v>
-      </c>
-      <c r="H16" s="1">
-        <v>2659.348</v>
-      </c>
-      <c r="I16" s="1">
-        <v>191.25450000000001</v>
-      </c>
-      <c r="L16" s="1">
-        <v>725.94880000000001</v>
-      </c>
-      <c r="M16" s="1">
-        <v>30</v>
-      </c>
-      <c r="N16" s="1">
-        <v>1525</v>
-      </c>
-      <c r="O16" s="1">
-        <v>160</v>
-      </c>
-      <c r="P16" s="1">
-        <v>430.0256</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+        <v>5140.2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>2308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>42369</v>
       </c>
-      <c r="E17" s="1">
-        <v>12459.52</v>
+      <c r="E17" s="6">
+        <v>9002.3989999999994</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1142.03</v>
       </c>
       <c r="G17" s="1">
-        <v>5000</v>
-      </c>
-      <c r="H17" s="1">
-        <v>3400</v>
-      </c>
-      <c r="I17" s="1">
-        <v>121.0758</v>
-      </c>
-      <c r="L17" s="1">
-        <v>1795.348</v>
-      </c>
-      <c r="M17" s="1">
-        <v>120</v>
-      </c>
-      <c r="N17" s="1">
-        <v>1900</v>
-      </c>
-      <c r="P17" s="1">
-        <v>123.0916</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+        <v>4520.5290000000005</v>
+      </c>
+      <c r="J17" s="1">
+        <v>2437.84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>42735</v>
       </c>
-      <c r="E18" s="1">
-        <v>12124.01</v>
+      <c r="E18" s="6">
+        <v>12172.2</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1472</v>
       </c>
       <c r="G18" s="1">
-        <v>4139.201</v>
-      </c>
-      <c r="H18" s="1">
-        <v>4742.835</v>
-      </c>
-      <c r="I18" s="1">
-        <v>693.03740000000005</v>
-      </c>
-      <c r="L18" s="1">
-        <v>200</v>
-      </c>
-      <c r="M18" s="1">
-        <v>80</v>
-      </c>
-      <c r="N18" s="1">
-        <v>2120</v>
-      </c>
-      <c r="P18" s="1">
-        <v>148.9402</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+        <v>4497.8999999999996</v>
+      </c>
+      <c r="J18" s="1">
+        <v>3452.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>43100</v>
       </c>
-      <c r="E19" s="1">
-        <v>14628.04</v>
+      <c r="E19" s="6">
+        <v>25439.599999999999</v>
+      </c>
+      <c r="F19" s="1">
+        <v>4245</v>
       </c>
       <c r="G19" s="1">
-        <v>7000</v>
-      </c>
-      <c r="H19" s="1">
-        <v>4251.4920000000002</v>
-      </c>
-      <c r="I19" s="1">
-        <v>966.62620000000004</v>
-      </c>
-      <c r="L19" s="1">
-        <v>140</v>
-      </c>
-      <c r="M19" s="1">
-        <v>70</v>
-      </c>
-      <c r="N19" s="1">
-        <v>1700</v>
-      </c>
-      <c r="P19" s="1">
-        <v>499.92230000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+        <v>11735</v>
+      </c>
+      <c r="J19" s="1">
+        <v>5109.6000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>43465</v>
       </c>
-      <c r="E20" s="1">
-        <v>19381.740000000002</v>
+      <c r="E20" s="6">
+        <v>23061.75</v>
       </c>
       <c r="F20" s="1">
-        <v>3826.0390000000002</v>
+        <v>4881.75</v>
       </c>
       <c r="G20" s="1">
-        <v>9093.8459999999995</v>
-      </c>
-      <c r="H20" s="1">
-        <v>5757</v>
+        <v>7000</v>
       </c>
       <c r="I20" s="1">
-        <v>676.28710000000001</v>
+        <v>3000</v>
       </c>
       <c r="J20" s="1">
-        <v>1432</v>
-      </c>
-      <c r="M20" s="1">
-        <v>100</v>
-      </c>
-      <c r="N20" s="1">
-        <v>3200</v>
-      </c>
-      <c r="P20" s="1">
-        <v>554.6078</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+        <v>4880</v>
+      </c>
+      <c r="K20" s="1">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>43830</v>
       </c>
-      <c r="E21" s="1">
-        <v>19091.28</v>
+      <c r="E21" s="6">
+        <v>20050</v>
       </c>
       <c r="F21" s="1">
-        <v>1448.0129999999999</v>
+        <v>4000</v>
       </c>
       <c r="G21" s="1">
-        <v>8184.4610000000002</v>
-      </c>
-      <c r="H21" s="1">
-        <v>5469.15</v>
+        <v>7800</v>
       </c>
       <c r="I21" s="1">
-        <v>177.25489999999999</v>
+        <v>2000</v>
       </c>
       <c r="J21" s="1">
-        <v>22</v>
-      </c>
-      <c r="M21" s="1">
-        <v>70</v>
-      </c>
-      <c r="N21" s="1">
-        <v>3296</v>
-      </c>
-      <c r="P21" s="1">
-        <v>424.39920000000001</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+        <v>4050</v>
+      </c>
+      <c r="K21" s="1">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>44196</v>
       </c>
-      <c r="E22" s="1">
-        <v>18953.82</v>
+      <c r="E22" s="6">
+        <v>21600</v>
       </c>
       <c r="F22" s="1">
-        <v>2845</v>
+        <v>3000</v>
       </c>
       <c r="G22" s="1">
-        <v>8000</v>
+        <v>7900</v>
       </c>
       <c r="H22" s="1">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="I22" s="1">
-        <v>287.64109999999999</v>
-      </c>
-      <c r="J22" s="1">
-        <v>27</v>
+        <v>900</v>
+      </c>
+      <c r="K22" s="1">
+        <v>2100</v>
       </c>
       <c r="M22" s="1">
-        <v>60</v>
-      </c>
-      <c r="N22" s="1">
-        <v>2966.4</v>
-      </c>
-      <c r="P22" s="1">
-        <v>267.77449999999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3900</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>44561</v>
       </c>
-      <c r="E23" s="1">
-        <v>28047.88</v>
+      <c r="E23" s="6">
+        <v>29600</v>
       </c>
       <c r="F23" s="1">
-        <v>1991.5</v>
+        <v>4000</v>
       </c>
       <c r="G23" s="1">
-        <v>12000</v>
+        <v>11200</v>
       </c>
       <c r="H23" s="1">
-        <v>7950</v>
+        <v>3700</v>
       </c>
       <c r="I23" s="1">
-        <v>403.0258</v>
-      </c>
-      <c r="J23" s="1">
-        <v>18.899999999999999</v>
+        <v>1100</v>
+      </c>
+      <c r="K23" s="1">
+        <v>3100</v>
       </c>
       <c r="M23" s="1">
-        <v>48</v>
-      </c>
-      <c r="N23" s="1">
-        <v>5300</v>
-      </c>
-      <c r="P23" s="1">
-        <v>336.45139999999998</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>44926</v>
       </c>
-      <c r="E24" s="1">
-        <v>30035.93</v>
+      <c r="E24" s="6">
+        <v>32395</v>
       </c>
       <c r="F24" s="1">
-        <v>4340.607</v>
+        <v>4450</v>
       </c>
       <c r="G24" s="1">
-        <v>11700</v>
+        <v>12200</v>
       </c>
       <c r="H24" s="1">
-        <v>6757.5</v>
-      </c>
-      <c r="I24" s="1">
-        <v>694.64340000000004</v>
-      </c>
-      <c r="J24" s="1">
-        <v>15</v>
+        <v>4650</v>
+      </c>
+      <c r="K24" s="1">
+        <v>4800</v>
+      </c>
+      <c r="L24" s="1">
+        <v>795</v>
       </c>
       <c r="M24" s="1">
-        <v>55</v>
-      </c>
-      <c r="N24" s="1">
-        <v>5000</v>
-      </c>
-      <c r="P24" s="1">
-        <v>1473.181</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>45291</v>
       </c>
-      <c r="E25" s="1">
-        <v>19976.75</v>
+      <c r="E25" s="6">
+        <v>18200</v>
       </c>
       <c r="F25" s="1">
-        <v>2083.491</v>
+        <v>2000</v>
       </c>
       <c r="G25" s="1">
         <v>10000</v>
       </c>
       <c r="H25" s="1">
-        <v>4000</v>
-      </c>
-      <c r="I25" s="1">
-        <v>423.69080000000002</v>
-      </c>
-      <c r="J25" s="1">
-        <v>10.5</v>
+        <v>1800</v>
+      </c>
+      <c r="K25" s="1">
+        <v>2000</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1100</v>
       </c>
       <c r="M25" s="1">
-        <v>41.8</v>
-      </c>
-      <c r="N25" s="1">
-        <v>3000</v>
-      </c>
-      <c r="P25" s="1">
-        <v>417.27120000000002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>45657</v>
       </c>
-      <c r="E26" s="1">
-        <v>29734.28</v>
+      <c r="E26" s="6">
+        <v>19500</v>
       </c>
       <c r="F26" s="1">
-        <v>3800</v>
+        <v>1800</v>
       </c>
       <c r="G26" s="1">
-        <v>13500</v>
+        <v>9500</v>
       </c>
       <c r="H26" s="1">
-        <v>6400</v>
-      </c>
-      <c r="I26" s="1">
-        <v>502.83550000000002</v>
-      </c>
-      <c r="J26" s="1">
-        <v>8.9250000000000007</v>
+        <v>2300</v>
+      </c>
+      <c r="K26" s="1">
+        <v>1800</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1100</v>
       </c>
       <c r="M26" s="1">
-        <v>39.71</v>
-      </c>
-      <c r="N26" s="1">
-        <v>5000</v>
-      </c>
-      <c r="P26" s="1">
-        <v>482.80680000000001</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>46022</v>
       </c>
-      <c r="E27" s="1">
-        <v>53700</v>
+      <c r="E27" s="6">
+        <v>21100</v>
       </c>
       <c r="F27" s="1">
-        <v>6500</v>
+        <v>2200</v>
       </c>
       <c r="G27" s="1">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="H27" s="1">
-        <v>17500</v>
-      </c>
-      <c r="I27" s="1">
-        <v>429.70409999999998</v>
-      </c>
-      <c r="J27" s="1">
-        <v>20</v>
+        <v>3200</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1600</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1200</v>
       </c>
       <c r="M27" s="1">
-        <v>42</v>
-      </c>
-      <c r="N27" s="1">
-        <v>11000</v>
-      </c>
-      <c r="P27" s="1">
-        <v>176.37110000000001</v>
+        <v>3900</v>
       </c>
     </row>
   </sheetData>
@@ -7461,22 +7667,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1809E1-8742-45D5-8384-0B8CBD4B91B0}">
   <dimension ref="A1:P27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.1640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" style="1"/>
-    <col min="8" max="8" width="9.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="8.83203125" style="1"/>
-    <col min="15" max="15" width="9.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="10.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.81640625" style="1"/>
+    <col min="8" max="8" width="9.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="8.81640625" style="1"/>
+    <col min="15" max="15" width="9.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>41</v>
       </c>
@@ -7526,87 +7732,87 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>36891</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>37256</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>37621</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>37986</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>38352</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>38717</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>39082</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>39447</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>39813</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>40178</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>40543</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>40908</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>41274</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>41639</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>42004</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="3">
         <v>42369</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="3">
         <v>42735</v>
       </c>
@@ -7614,7 +7820,7 @@
         <v>10105</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>43100</v>
       </c>
@@ -7622,7 +7828,7 @@
         <v>11127</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>43465</v>
       </c>
@@ -7654,7 +7860,7 @@
         <v>650.73940000000005</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>43830</v>
       </c>
@@ -7692,7 +7898,7 @@
         <v>534.69730000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>44196</v>
       </c>
@@ -7730,7 +7936,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>44561</v>
       </c>
@@ -7768,7 +7974,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>44926</v>
       </c>
@@ -7809,7 +8015,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>45291</v>
       </c>
@@ -7850,7 +8056,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>45657</v>
       </c>
@@ -7891,7 +8097,7 @@
         <v>2858</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>46022</v>
       </c>
@@ -7940,7 +8146,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1ACCD2-1A48-4153-9D3A-8CF140E4CA91}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -7950,12 +8156,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{365F0AC2-65A4-4AE7-B202-A8AA169AE8AB}">
   <dimension ref="A2:C32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>5</v>
       </c>
@@ -7963,7 +8169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -7974,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -7982,7 +8188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -7990,7 +8196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -7998,7 +8204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>11</v>
       </c>
@@ -8006,7 +8212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>12</v>
       </c>
@@ -8014,7 +8220,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -8025,7 +8231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>17</v>
       </c>
@@ -8033,7 +8239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>8</v>
       </c>
@@ -8041,7 +8247,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>0</v>
       </c>
@@ -8049,7 +8255,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>22</v>
       </c>
@@ -8057,7 +8263,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -8065,7 +8271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>26</v>
       </c>
@@ -8073,7 +8279,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>29</v>
       </c>
@@ -8081,7 +8287,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>31</v>
       </c>
@@ -8089,7 +8295,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>12</v>
       </c>
@@ -8097,7 +8303,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>34</v>
       </c>
@@ -8105,7 +8311,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>35</v>
       </c>
@@ -8113,7 +8319,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>38</v>
       </c>
@@ -8124,7 +8330,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>45</v>
       </c>
@@ -8132,12 +8338,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>8</v>
       </c>
@@ -8145,7 +8351,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>50</v>
       </c>
@@ -8153,7 +8359,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>31</v>
       </c>
@@ -8161,7 +8367,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>26</v>
       </c>
@@ -8169,7 +8375,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>54</v>
       </c>
@@ -8177,7 +8383,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>57</v>
       </c>
@@ -8185,7 +8391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>59</v>
       </c>
@@ -8193,7 +8399,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>61</v>
       </c>
@@ -8201,7 +8407,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>63</v>
       </c>
